--- a/schedule-Fall26.xlsx
+++ b/schedule-Fall26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexander/GitHub/abuabara.github.io/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abuabara/GitHub/abuabara.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607241C4-75D6-404E-BEF8-CFD3331F817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4760" yWindow="640" windowWidth="25480" windowHeight="15440" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
+    <workbookView xWindow="0" yWindow="520" windowWidth="22940" windowHeight="14380" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/schedule-Fall26.xlsx
+++ b/schedule-Fall26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abuabara/GitHub/abuabara.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607241C4-75D6-404E-BEF8-CFD3331F817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8D30E9-6286-374B-A4A8-E0A5DC927EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="520" windowWidth="22940" windowHeight="14380" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
+    <workbookView xWindow="6700" yWindow="520" windowWidth="16240" windowHeight="14380" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="62">
   <si>
     <t>M</t>
   </si>
@@ -110,48 +110,6 @@
     <t>Introduction</t>
   </si>
   <si>
-    <t>Team Formation &amp; Sponsor Matching</t>
-  </si>
-  <si>
-    <t>Problem Definition &amp; Project Charter</t>
-  </si>
-  <si>
-    <t>Requirements Engineering</t>
-  </si>
-  <si>
-    <t>Data Acquisition &amp; Source Evaluation</t>
-  </si>
-  <si>
-    <t>Ethics, Privacy, &amp; Responsible Data Use</t>
-  </si>
-  <si>
-    <t>System Architecture Design</t>
-  </si>
-  <si>
-    <t>Design Constraints &amp; Applicable Standards</t>
-  </si>
-  <si>
-    <t>Project Management &amp; Agile Planning</t>
-  </si>
-  <si>
-    <t>Initial Technical Prototype</t>
-  </si>
-  <si>
-    <t>Technical Writing &amp; Documentation</t>
-  </si>
-  <si>
-    <t>Oral &amp; Visual Presentation Skills</t>
-  </si>
-  <si>
-    <t>Midpoint Design Review</t>
-  </si>
-  <si>
-    <t>Final Proposal Preparation</t>
-  </si>
-  <si>
-    <t>Final Presentations</t>
-  </si>
-  <si>
     <t>Bayesian thinking for risk and decision analysis</t>
   </si>
   <si>
@@ -201,6 +159,69 @@
   </si>
   <si>
     <t>DAEN300</t>
+  </si>
+  <si>
+    <t>Team formation (part 1)</t>
+  </si>
+  <si>
+    <t>Sponsor matching</t>
+  </si>
+  <si>
+    <t>Decompose a problem (V model)</t>
+  </si>
+  <si>
+    <t>Decompose a problem (Toaster)</t>
+  </si>
+  <si>
+    <t>About reports (Toasters)</t>
+  </si>
+  <si>
+    <t>Project charter</t>
+  </si>
+  <si>
+    <t>Problem definition</t>
+  </si>
+  <si>
+    <t>Requirements engineering</t>
+  </si>
+  <si>
+    <t>Standards engineering</t>
+  </si>
+  <si>
+    <t>Data acquisition / source evaluation</t>
+  </si>
+  <si>
+    <t>Advisor(s)</t>
+  </si>
+  <si>
+    <t>Ethics, privacy, and responsible data use</t>
+  </si>
+  <si>
+    <t>System architecture design</t>
+  </si>
+  <si>
+    <t>Design constraints and applicable standards</t>
+  </si>
+  <si>
+    <t>Project management (and Agile planning)</t>
+  </si>
+  <si>
+    <t>Initial technical prototype</t>
+  </si>
+  <si>
+    <t>Technical writing and documentation</t>
+  </si>
+  <si>
+    <t>Oral and visual presentation skills</t>
+  </si>
+  <si>
+    <t>Midpoint design review</t>
+  </si>
+  <si>
+    <t>Final proposal preparation</t>
+  </si>
+  <si>
+    <t>Final presentations</t>
   </si>
 </sst>
 </file>
@@ -671,13 +692,13 @@
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="9" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -691,7 +712,7 @@
         <v>46258</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>23</v>
@@ -708,6 +729,9 @@
       <c r="C3" s="4">
         <v>46260</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="F3" s="10" t="s">
         <v>18</v>
       </c>
@@ -721,7 +745,9 @@
         <v>46262</v>
       </c>
       <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="E4" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6">
@@ -735,10 +761,10 @@
         <v>46265</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>18</v>
@@ -752,6 +778,9 @@
       <c r="C6" s="4">
         <v>46267</v>
       </c>
+      <c r="E6" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="F6" s="10" t="s">
         <v>18</v>
       </c>
@@ -765,7 +794,9 @@
         <v>46269</v>
       </c>
       <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
+      <c r="E7" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6">
@@ -779,10 +810,10 @@
         <v>46272</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>18</v>
@@ -796,6 +827,9 @@
       <c r="C9" s="4">
         <v>46274</v>
       </c>
+      <c r="E9" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="F9" s="10" t="s">
         <v>18</v>
       </c>
@@ -809,7 +843,9 @@
         <v>46276</v>
       </c>
       <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6">
@@ -823,10 +859,10 @@
         <v>46279</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>18</v>
@@ -840,6 +876,9 @@
       <c r="C12" s="4">
         <v>46281</v>
       </c>
+      <c r="E12" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F12" s="10" t="s">
         <v>18</v>
       </c>
@@ -853,7 +892,9 @@
         <v>46283</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="E13" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6">
@@ -867,10 +908,10 @@
         <v>46286</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>18</v>
@@ -914,7 +955,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>18</v>
@@ -929,7 +970,7 @@
         <v>46295</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>18</v>
@@ -958,10 +999,10 @@
         <v>46300</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>18</v>
@@ -1002,10 +1043,10 @@
         <v>46307</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>18</v>
@@ -1046,10 +1087,10 @@
         <v>46314</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>18</v>
@@ -1090,10 +1131,10 @@
         <v>46321</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>18</v>
@@ -1134,10 +1175,10 @@
         <v>46328</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>18</v>
@@ -1181,7 +1222,7 @@
         <v>21</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>18</v>
@@ -1196,7 +1237,7 @@
         <v>46337</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>18</v>
@@ -1225,10 +1266,10 @@
         <v>46342</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>18</v>
@@ -1269,10 +1310,10 @@
         <v>46349</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>18</v>
@@ -1338,7 +1379,7 @@
         <v>22</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1351,7 +1392,7 @@
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="13" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="F46" s="11" t="s">
         <v>18</v>

--- a/schedule-Fall26.xlsx
+++ b/schedule-Fall26.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8D30E9-6286-374B-A4A8-E0A5DC927EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6700" yWindow="520" windowWidth="16240" windowHeight="14380" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
+    <workbookView xWindow="46660" yWindow="240" windowWidth="27800" windowHeight="14380" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/schedule-Fall26.xlsx
+++ b/schedule-Fall26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abuabara/GitHub/abuabara.github.io/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexander/GitHub/abuabara.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8D30E9-6286-374B-A4A8-E0A5DC927EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BF807B-5B14-3046-A9C4-5A435E0C802E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46660" yWindow="240" windowWidth="27800" windowHeight="14380" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16980" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
   <si>
     <t>M</t>
   </si>
@@ -222,6 +222,54 @@
   </si>
   <si>
     <t>Final presentations</t>
+  </si>
+  <si>
+    <t>(Python and Jupyter) Functions, debugging, profiling</t>
+  </si>
+  <si>
+    <t>Mini-project: Data prep -&gt; ML  -&gt; optimization</t>
+  </si>
+  <si>
+    <t>Optimization: backtracking, dynamic programming</t>
+  </si>
+  <si>
+    <t>Clustering, PCA, model selection</t>
+  </si>
+  <si>
+    <t>Decision trees, random forests, tree traversal</t>
+  </si>
+  <si>
+    <t>Classification, model evaluation</t>
+  </si>
+  <si>
+    <t>Linear regression</t>
+  </si>
+  <si>
+    <t>(Scikit-Learn) Machine learning basics</t>
+  </si>
+  <si>
+    <t>(Matplotlib) Visualization and exploratory analysis</t>
+  </si>
+  <si>
+    <t>Algorithms: binary search, merge sort, quick sort</t>
+  </si>
+  <si>
+    <t>Recursive + iterative solutions, base cases, call stacks</t>
+  </si>
+  <si>
+    <t>Data transformation: grouping, pivot tables, strings</t>
+  </si>
+  <si>
+    <t>(pandas) DataFrames, filtering, missing data, joins</t>
+  </si>
+  <si>
+    <t>(NumPy) Arrays, indexing, vectorization, aggregation</t>
+  </si>
+  <si>
+    <t>" "</t>
+  </si>
+  <si>
+    <t>Wrap-up</t>
   </si>
 </sst>
 </file>
@@ -683,8 +731,8 @@
   <cols>
     <col min="1" max="3" width="8.1640625" customWidth="1"/>
     <col min="4" max="4" width="46.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -729,6 +777,9 @@
       <c r="C3" s="4">
         <v>46260</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>44</v>
       </c>
@@ -744,11 +795,15 @@
       <c r="C4" s="6">
         <v>46262</v>
       </c>
-      <c r="D4" s="7"/>
+      <c r="D4" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
@@ -778,6 +833,9 @@
       <c r="C6" s="4">
         <v>46267</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="E6" s="1" t="s">
         <v>43</v>
       </c>
@@ -793,11 +851,15 @@
       <c r="C7" s="6">
         <v>46269</v>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="7"/>
+      <c r="F7" s="7" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
@@ -827,6 +889,9 @@
       <c r="C9" s="4">
         <v>46274</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>47</v>
       </c>
@@ -842,11 +907,15 @@
       <c r="C10" s="6">
         <v>46276</v>
       </c>
-      <c r="D10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="7"/>
+      <c r="F10" s="7" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
@@ -876,6 +945,9 @@
       <c r="C12" s="4">
         <v>46281</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="E12" s="1" t="s">
         <v>48</v>
       </c>
@@ -891,11 +963,15 @@
       <c r="C13" s="6">
         <v>46283</v>
       </c>
-      <c r="D13" s="7"/>
+      <c r="D13" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="7"/>
+      <c r="F13" s="7" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
@@ -925,6 +1001,9 @@
       <c r="C15" s="4">
         <v>46288</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="F15" s="10" t="s">
         <v>18</v>
       </c>
@@ -937,9 +1016,13 @@
       <c r="C16" s="6">
         <v>46290</v>
       </c>
-      <c r="D16" s="7"/>
+      <c r="D16" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="F16" s="7" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
@@ -984,9 +1067,13 @@
       <c r="C19" s="6">
         <v>46297</v>
       </c>
-      <c r="D19" s="7"/>
+      <c r="D19" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="F19" s="7" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
@@ -1016,6 +1103,9 @@
       <c r="C21" s="4">
         <v>46302</v>
       </c>
+      <c r="D21" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="F21" s="10" t="s">
         <v>18</v>
       </c>
@@ -1028,9 +1118,13 @@
       <c r="C22" s="6">
         <v>46304</v>
       </c>
-      <c r="D22" s="7"/>
+      <c r="D22" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="F22" s="7" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
@@ -1060,6 +1154,9 @@
       <c r="C24" s="4">
         <v>46309</v>
       </c>
+      <c r="D24" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="F24" s="10" t="s">
         <v>18</v>
       </c>
@@ -1072,9 +1169,13 @@
       <c r="C25" s="6">
         <v>46311</v>
       </c>
-      <c r="D25" s="7"/>
+      <c r="D25" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="F25" s="7" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3" t="s">
@@ -1104,6 +1205,9 @@
       <c r="C27" s="4">
         <v>46316</v>
       </c>
+      <c r="D27" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="F27" s="10" t="s">
         <v>18</v>
       </c>
@@ -1116,9 +1220,13 @@
       <c r="C28" s="6">
         <v>46318</v>
       </c>
-      <c r="D28" s="7"/>
+      <c r="D28" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
+      <c r="F28" s="7" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
@@ -1148,6 +1256,9 @@
       <c r="C30" s="4">
         <v>46323</v>
       </c>
+      <c r="D30" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="F30" s="10" t="s">
         <v>18</v>
       </c>
@@ -1160,9 +1271,13 @@
       <c r="C31" s="6">
         <v>46325</v>
       </c>
-      <c r="D31" s="7"/>
+      <c r="D31" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
+      <c r="F31" s="7" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="3" t="s">
@@ -1192,6 +1307,9 @@
       <c r="C33" s="4">
         <v>46330</v>
       </c>
+      <c r="D33" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="F33" s="10" t="s">
         <v>18</v>
       </c>
@@ -1204,9 +1322,13 @@
       <c r="C34" s="6">
         <v>46332</v>
       </c>
-      <c r="D34" s="7"/>
+      <c r="D34" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
+      <c r="F34" s="7" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3" t="s">
@@ -1251,9 +1373,13 @@
       <c r="C37" s="6">
         <v>46339</v>
       </c>
-      <c r="D37" s="7"/>
+      <c r="D37" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
+      <c r="F37" s="7" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="3" t="s">
@@ -1283,6 +1409,9 @@
       <c r="C39" s="4">
         <v>46344</v>
       </c>
+      <c r="D39" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="F39" s="10" t="s">
         <v>18</v>
       </c>
@@ -1295,9 +1424,13 @@
       <c r="C40" s="6">
         <v>46346</v>
       </c>
-      <c r="D40" s="7"/>
+      <c r="D40" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
+      <c r="F40" s="7" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="3" t="s">
@@ -1351,7 +1484,9 @@
       <c r="E43" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F43" s="7"/>
+      <c r="F43" s="7" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3" t="s">
@@ -1362,6 +1497,12 @@
       </c>
       <c r="C44" s="4">
         <v>46356</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="F44" s="10" t="s">
         <v>18</v>
@@ -1381,6 +1522,9 @@
       <c r="E45" s="12" t="s">
         <v>61</v>
       </c>
+      <c r="F45" s="1" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="5"/>
@@ -1390,7 +1534,9 @@
       <c r="C46" s="6">
         <v>46358</v>
       </c>
-      <c r="D46" s="7"/>
+      <c r="D46" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="E46" s="13" t="s">
         <v>61</v>
       </c>

--- a/schedule-Fall26.xlsx
+++ b/schedule-Fall26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexander/GitHub/abuabara.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BF807B-5B14-3046-A9C4-5A435E0C802E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F17639-2CD3-4A4B-8408-872A27200D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16980" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="27040" windowHeight="16980" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="95">
   <si>
     <t>M</t>
   </si>
@@ -152,15 +152,6 @@
     <t>Bayesian decision analysis and probabilistic forecasting</t>
   </si>
   <si>
-    <t>DAEN/ISEN427-ISEN627</t>
-  </si>
-  <si>
-    <t>DAEN459</t>
-  </si>
-  <si>
-    <t>DAEN300</t>
-  </si>
-  <si>
     <t>Team formation (part 1)</t>
   </si>
   <si>
@@ -270,13 +261,73 @@
   </si>
   <si>
     <t>Wrap-up</t>
+  </si>
+  <si>
+    <t>DAEN 460</t>
+  </si>
+  <si>
+    <t>DAEN 459</t>
+  </si>
+  <si>
+    <t>DAEN/ISEN 427 / ISEN 627</t>
+  </si>
+  <si>
+    <t>DAEN 300</t>
+  </si>
+  <si>
+    <t>DAEN 301</t>
+  </si>
+  <si>
+    <t>Reproducible stochastic computation: random variables, distributions, random-number generators, seeds</t>
+  </si>
+  <si>
+    <t>Monte Carlo simulation: sampling, estimation, confidence intervals, convergence</t>
+  </si>
+  <si>
+    <t>Stochastic processes: random walks, state transitions, Markov chains</t>
+  </si>
+  <si>
+    <t>Discrete-event simulation: queues, events, system performance and sensitivity analysis</t>
+  </si>
+  <si>
+    <t>Ensemble foundations: bias–variance tradeoff, resampling, bootstrap aggregation</t>
+  </si>
+  <si>
+    <t>Bagging and randomized ensembles: random forests, Extra Trees, out-of-bag evaluation</t>
+  </si>
+  <si>
+    <t>Boosting: AdaBoost, gradient boosting, learning rates and early stopping</t>
+  </si>
+  <si>
+    <t>Combining models: voting, stacking, calibration and leakage-safe evaluation</t>
+  </si>
+  <si>
+    <t>Reinforcement-learning foundations: agents, environments, states, actions, rewards</t>
+  </si>
+  <si>
+    <t>Multi-armed bandits: exploration versus exploitation, ε-greedy and UCB</t>
+  </si>
+  <si>
+    <t>Markov decision processes: policies, returns, value functions and Bellman equations</t>
+  </si>
+  <si>
+    <t>Dynamic-programming methods: policy evaluation, policy iteration and value iteration</t>
+  </si>
+  <si>
+    <t>Model-free reinforcement learning: Monte Carlo, temporal-difference and Q-learning</t>
+  </si>
+  <si>
+    <t>Data visualization and communication: uncertainty, model comparison, interactive dashboards</t>
+  </si>
+  <si>
+    <t>Mini-project: stochastic system → ensemble or RL solution → visual explanation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -306,6 +357,11 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -363,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -392,6 +448,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -726,30 +783,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8F4810-9FE7-B94E-996A-E85E66BE30A5}">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="3" width="8.1640625" customWidth="1"/>
-    <col min="4" max="4" width="46.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="46.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="87.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="9" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>75</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,11 +827,14 @@
       <c r="E2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>1</v>
@@ -778,16 +843,19 @@
         <v>46260</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>41</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
         <v>2</v>
@@ -796,16 +864,20 @@
         <v>46262</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>42</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -819,13 +891,16 @@
         <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>38</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>1</v>
@@ -834,16 +909,19 @@
         <v>46267</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>40</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>2</v>
@@ -852,16 +930,20 @@
         <v>46269</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>39</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
@@ -875,13 +957,16 @@
         <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>43</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>1</v>
@@ -890,16 +975,19 @@
         <v>46274</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>44</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
         <v>2</v>
@@ -908,16 +996,20 @@
         <v>46276</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>48</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="3" t="s">
         <v>6</v>
       </c>
@@ -931,13 +1023,16 @@
         <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>38</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>1</v>
@@ -946,16 +1041,19 @@
         <v>46281</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>45</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
         <v>2</v>
@@ -964,16 +1062,20 @@
         <v>46283</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>46</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="3" t="s">
         <v>7</v>
       </c>
@@ -987,13 +1089,16 @@
         <v>28</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>47</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>1</v>
@@ -1002,13 +1107,16 @@
         <v>46288</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>73</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
         <v>2</v>
@@ -1017,14 +1125,18 @@
         <v>46290</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E16" s="7"/>
-      <c r="F16" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="F16" s="7"/>
+      <c r="G16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1038,13 +1150,16 @@
         <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>49</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>1</v>
@@ -1055,11 +1170,14 @@
       <c r="D18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
         <v>2</v>
@@ -1068,14 +1186,18 @@
         <v>46297</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E19" s="7"/>
-      <c r="F19" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="F19" s="7"/>
+      <c r="G19" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="3" t="s">
         <v>9</v>
       </c>
@@ -1089,13 +1211,16 @@
         <v>30</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>50</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>1</v>
@@ -1104,13 +1229,16 @@
         <v>46302</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>73</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
         <v>2</v>
@@ -1119,14 +1247,18 @@
         <v>46304</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E22" s="7"/>
-      <c r="F22" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="F22" s="7"/>
+      <c r="G22" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="3" t="s">
         <v>10</v>
       </c>
@@ -1140,13 +1272,16 @@
         <v>31</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>51</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>1</v>
@@ -1155,13 +1290,16 @@
         <v>46309</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>73</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
         <v>2</v>
@@ -1170,14 +1308,18 @@
         <v>46311</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E25" s="7"/>
-      <c r="F25" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="F25" s="7"/>
+      <c r="G25" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="3" t="s">
         <v>11</v>
       </c>
@@ -1191,13 +1333,16 @@
         <v>32</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>52</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>1</v>
@@ -1206,13 +1351,16 @@
         <v>46316</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>73</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="5"/>
       <c r="B28" s="5" t="s">
         <v>2</v>
@@ -1221,14 +1369,18 @@
         <v>46318</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E28" s="7"/>
-      <c r="F28" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="F28" s="7"/>
+      <c r="G28" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="3" t="s">
         <v>12</v>
       </c>
@@ -1242,13 +1394,16 @@
         <v>33</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>53</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>1</v>
@@ -1257,13 +1412,16 @@
         <v>46323</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>73</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
         <v>2</v>
@@ -1272,14 +1430,18 @@
         <v>46325</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E31" s="7"/>
-      <c r="F31" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="F31" s="7"/>
+      <c r="G31" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="3" t="s">
         <v>13</v>
       </c>
@@ -1293,13 +1455,16 @@
         <v>34</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>54</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>1</v>
@@ -1308,13 +1473,16 @@
         <v>46330</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>73</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
         <v>2</v>
@@ -1323,14 +1491,18 @@
         <v>46332</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E34" s="7"/>
-      <c r="F34" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="F34" s="7"/>
+      <c r="G34" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="3" t="s">
         <v>14</v>
       </c>
@@ -1344,13 +1516,16 @@
         <v>21</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>55</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>1</v>
@@ -1361,11 +1536,14 @@
       <c r="D36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F36" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="G36" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="5"/>
       <c r="B37" s="5" t="s">
         <v>2</v>
@@ -1374,14 +1552,18 @@
         <v>46339</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E37" s="7"/>
-      <c r="F37" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="F37" s="7"/>
+      <c r="G37" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="3" t="s">
         <v>15</v>
       </c>
@@ -1395,13 +1577,17 @@
         <v>36</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>56</v>
+      </c>
+      <c r="F38" s="12"/>
+      <c r="G38" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>1</v>
@@ -1410,13 +1596,16 @@
         <v>46344</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>73</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
         <v>2</v>
@@ -1425,14 +1614,18 @@
         <v>46346</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E40" s="7"/>
-      <c r="F40" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="F40" s="7"/>
+      <c r="G40" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="3" t="s">
         <v>16</v>
       </c>
@@ -1446,13 +1639,16 @@
         <v>37</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>57</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>1</v>
@@ -1466,11 +1662,15 @@
       <c r="E42" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F42" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="F42" s="10"/>
+      <c r="G42" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
         <v>2</v>
@@ -1484,11 +1684,15 @@
       <c r="E43" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F43" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="F43" s="11"/>
+      <c r="G43" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="3" t="s">
         <v>17</v>
       </c>
@@ -1499,16 +1703,19 @@
         <v>46356</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>74</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>19</v>
@@ -1520,13 +1727,17 @@
         <v>22</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>58</v>
+      </c>
+      <c r="F45" s="12"/>
+      <c r="G45" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="5"/>
       <c r="B46" s="5" t="s">
         <v>1</v>
@@ -1535,12 +1746,16 @@
         <v>46358</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F46" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" s="13"/>
+      <c r="G46" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="11" t="s">
         <v>18</v>
       </c>
     </row>

--- a/schedule-Fall26.xlsx
+++ b/schedule-Fall26.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexander/GitHub/abuabara.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F17639-2CD3-4A4B-8408-872A27200D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66B1284-3406-5142-B2C8-F61A69296FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="27040" windowHeight="16980" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="27040" windowHeight="16980" activeTab="1" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="2026 Fall" sheetId="1" r:id="rId1"/>
+    <sheet name="DAEN 427" sheetId="4" r:id="rId2"/>
+    <sheet name="DAEN 300-301" sheetId="3" r:id="rId3"/>
+    <sheet name="DAEN Capstone" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="205">
   <si>
     <t>M</t>
   </si>
@@ -321,6 +324,336 @@
   </si>
   <si>
     <t>Mini-project: stochastic system → ensemble or RL solution → visual explanation</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Lecture topics</t>
+  </si>
+  <si>
+    <t>Team/lab activities</t>
+  </si>
+  <si>
+    <t>Milestone or deliverable</t>
+  </si>
+  <si>
+    <t>Capstone expectations; design process; professional conduct</t>
+  </si>
+  <si>
+    <t>Review sponsor projects; skills and interest inventory</t>
+  </si>
+  <si>
+    <t>Individual skills profile and project preferences</t>
+  </si>
+  <si>
+    <t>Team formation; teamwork; roles and responsibilities</t>
+  </si>
+  <si>
+    <t>Form teams; select projects; establish communication practices</t>
+  </si>
+  <si>
+    <t>Team agreement and preliminary role assignments</t>
+  </si>
+  <si>
+    <t>Sponsor engagement; stakeholder analysis; effective interviewing</t>
+  </si>
+  <si>
+    <t>Initial sponsor meeting; identify stakeholders and decision context</t>
+  </si>
+  <si>
+    <t>Sponsor meeting notes and stakeholder register</t>
+  </si>
+  <si>
+    <t>Problem framing; needs assessment; requirements elicitation</t>
+  </si>
+  <si>
+    <t>Translate sponsor needs into a preliminary problem statement</t>
+  </si>
+  <si>
+    <t>Problem statement and project objectives</t>
+  </si>
+  <si>
+    <t>Project charters; scope definition; assumptions and constraints</t>
+  </si>
+  <si>
+    <t>Define scope, exclusions, success criteria, and major deliverables</t>
+  </si>
+  <si>
+    <t>Draft project charter</t>
+  </si>
+  <si>
+    <t>Ethics, privacy, security, bias, and responsible data use</t>
+  </si>
+  <si>
+    <t>Conduct ethical and data-governance review</t>
+  </si>
+  <si>
+    <t>Ethics, privacy, and risk assessment</t>
+  </si>
+  <si>
+    <t>Data requirements; data provenance; acquisition strategies</t>
+  </si>
+  <si>
+    <t>Inventory available data; identify gaps and access dependencies</t>
+  </si>
+  <si>
+    <t>Data requirements and acquisition plan</t>
+  </si>
+  <si>
+    <t>Initial data collection and profiling</t>
+  </si>
+  <si>
+    <t>Acquire an initial dataset; assess schema, quality, completeness, and suitability</t>
+  </si>
+  <si>
+    <t>Initial data inventory and profiling report</t>
+  </si>
+  <si>
+    <t>Data engineering architecture and tool selection</t>
+  </si>
+  <si>
+    <t>Develop source-to-output architecture; evaluate platforms and tools</t>
+  </si>
+  <si>
+    <t>Preliminary system/data architecture</t>
+  </si>
+  <si>
+    <t>Applicable standards; legal, organizational, and design constraints</t>
+  </si>
+  <si>
+    <t>Identify standards and convert constraints into requirements</t>
+  </si>
+  <si>
+    <t>Requirements and constraints matrix</t>
+  </si>
+  <si>
+    <t>Project management; work breakdown structures; estimation</t>
+  </si>
+  <si>
+    <t>Develop tasks, dependencies, schedule, ownership, and communication plan</t>
+  </si>
+  <si>
+    <t>Work breakdown structure and project schedule</t>
+  </si>
+  <si>
+    <t>Risk management; feasibility; change control</t>
+  </si>
+  <si>
+    <t>Assess technical, data, schedule, personnel, and sponsor risks</t>
+  </si>
+  <si>
+    <t>Risk register and mitigation plan</t>
+  </si>
+  <si>
+    <t>Evaluation planning; alternatives; metrics and acceptance criteria</t>
+  </si>
+  <si>
+    <t>Define baseline, alternatives, validation methods, and performance measures</t>
+  </si>
+  <si>
+    <t>Evaluation and verification plan</t>
+  </si>
+  <si>
+    <t>Technical writing; visual communication; design reviews</t>
+  </si>
+  <si>
+    <t>Integrate planning artifacts; peer and instructor design review</t>
+  </si>
+  <si>
+    <t>Draft planning report and presentation</t>
+  </si>
+  <si>
+    <t>Professional presentations; transition to implementation</t>
+  </si>
+  <si>
+    <t>Formal sponsor presentation; revise plans based on feedback</t>
+  </si>
+  <si>
+    <t>Final planning report, charter, presentation, and DAEN 460 transition package</t>
+  </si>
+  <si>
+    <t>Project reactivation; execution expectations; configuration management</t>
+  </si>
+  <si>
+    <t>Reconfirm scope, roles, sponsor expectations, data access, and schedule</t>
+  </si>
+  <si>
+    <t>Updated project plan and kickoff memorandum</t>
+  </si>
+  <si>
+    <t>Reproducible development; repositories; testing strategy</t>
+  </si>
+  <si>
+    <t>Configure development environment, repository workflow, and issue tracking</t>
+  </si>
+  <si>
+    <t>Reproducibility and testing plan</t>
+  </si>
+  <si>
+    <t>Data ingestion and acquisition</t>
+  </si>
+  <si>
+    <t>Implement source connections and initial ingestion processes</t>
+  </si>
+  <si>
+    <t>Working ingestion prototype</t>
+  </si>
+  <si>
+    <t>Data quality engineering; validation and observability</t>
+  </si>
+  <si>
+    <t>Implement schema, completeness, accuracy, and anomaly checks</t>
+  </si>
+  <si>
+    <t>Data-quality rules and baseline assessment</t>
+  </si>
+  <si>
+    <t>Data transformation; integration; metadata and lineage</t>
+  </si>
+  <si>
+    <t>Build repeatable cleaning, transformation, and integration workflows</t>
+  </si>
+  <si>
+    <t>Storage, data modeling, performance, and security</t>
+  </si>
+  <si>
+    <t>Implement storage/modeling layer; review access controls</t>
+  </si>
+  <si>
+    <t>Architecture and implementation review</t>
+  </si>
+  <si>
+    <t>Exploratory analysis; baselines; analytical validity</t>
+  </si>
+  <si>
+    <t>Establish descriptive findings and baseline performance</t>
+  </si>
+  <si>
+    <t>Technical progress report 1</t>
+  </si>
+  <si>
+    <t>Midsemester design review</t>
+  </si>
+  <si>
+    <t>Demonstrate pipeline and preliminary analysis to faculty and sponsor</t>
+  </si>
+  <si>
+    <t>Application of analytical or data engineering methods</t>
+  </si>
+  <si>
+    <t>Implement primary models, algorithms, or decision-support methods</t>
+  </si>
+  <si>
+    <t>Analysis/modeling increment 1</t>
+  </si>
+  <si>
+    <t>Alternative designs; trade-off analysis; design constraints</t>
+  </si>
+  <si>
+    <t>Compare approaches using technical and stakeholder criteria</t>
+  </si>
+  <si>
+    <t>Alternatives and trade-off analysis</t>
+  </si>
+  <si>
+    <t>Verification, validation, testing, and uncertainty</t>
+  </si>
+  <si>
+    <t>Perform system tests, sensitivity analysis, error analysis, or model validation</t>
+  </si>
+  <si>
+    <t>Interpretation; recommendations; operational implications</t>
+  </si>
+  <si>
+    <t>Convert results into sponsor-relevant findings and recommendations</t>
+  </si>
+  <si>
+    <t>Draft findings and recommendations</t>
+  </si>
+  <si>
+    <t>Deployment, maintainability, documentation, and handoff</t>
+  </si>
+  <si>
+    <t>Package pipeline, code, dashboard, model, or other product for sponsor use</t>
+  </si>
+  <si>
+    <t>Release candidate and technical documentation</t>
+  </si>
+  <si>
+    <t>Report writing; presentation design; peer review</t>
+  </si>
+  <si>
+    <t>Conduct final technical review and rehearsal; resolve remaining defects</t>
+  </si>
+  <si>
+    <t>Final design presentation and project handoff</t>
+  </si>
+  <si>
+    <t>Present results; demonstrate product; transfer artifacts to sponsor</t>
+  </si>
+  <si>
+    <t>Python and Jupyter: functions, debugging and profiling</t>
+  </si>
+  <si>
+    <t>NumPy: arrays, indexing, vectorization and aggregation</t>
+  </si>
+  <si>
+    <t>pandas: DataFrames, filtering, missing data and joins</t>
+  </si>
+  <si>
+    <t>Data transformation: grouping, pivot tables and string operations</t>
+  </si>
+  <si>
+    <t>Recursive and iterative solutions: base cases and call stacks</t>
+  </si>
+  <si>
+    <t>Algorithms: binary search, merge sort and quicksort</t>
+  </si>
+  <si>
+    <t>Matplotlib: data visualization and exploratory analysis</t>
+  </si>
+  <si>
+    <t>scikit-learn: machine-learning fundamentals and workflow</t>
+  </si>
+  <si>
+    <t>Regression: linear regression and performance evaluation</t>
+  </si>
+  <si>
+    <t>Classification: classification methods and model evaluation</t>
+  </si>
+  <si>
+    <t>Tree-based methods: decision trees, random forests and tree traversal</t>
+  </si>
+  <si>
+    <t>Unsupervised learning: clustering, PCA and model selection</t>
+  </si>
+  <si>
+    <t>Optimization: backtracking and dynamic programming</t>
+  </si>
+  <si>
+    <t>Mini-project: data preparation → machine learning → optimization</t>
+  </si>
+  <si>
+    <t>Course wrap-up: integration, reflection and review</t>
+  </si>
+  <si>
+    <t>Topics</t>
+  </si>
+  <si>
+    <t>Final report, showcase presentation, product, repository, and sponsor handoff</t>
+  </si>
+  <si>
+    <t>Draft final report and PRESENTATION 4</t>
+  </si>
+  <si>
+    <t>Validation and testing report, PRESENTATION 3</t>
+  </si>
+  <si>
+    <t>End-to-end pipeline increment 1, PRESENTATION 1</t>
+  </si>
+  <si>
+    <t>Working prototype, Midterm PRESENTATION 2</t>
   </si>
 </sst>
 </file>
@@ -419,7 +752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -449,6 +782,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1764,4 +2099,865 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8039D520-0785-5A46-BDC3-81B2E34CFFB2}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="46.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D44D6C-8698-1045-8E5E-419F77891939}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="87.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>10</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F50E3AB-4B57-7045-B2A8-07BD4DBB8661}">
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="55.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" t="s">
+        <v>154</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>156</v>
+      </c>
+      <c r="C22" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>10</v>
+      </c>
+      <c r="B27" t="s">
+        <v>169</v>
+      </c>
+      <c r="C27" t="s">
+        <v>170</v>
+      </c>
+      <c r="D27" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C29" t="s">
+        <v>175</v>
+      </c>
+      <c r="D29" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>177</v>
+      </c>
+      <c r="C30" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C31" t="s">
+        <v>181</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/schedule-Fall26.xlsx
+++ b/schedule-Fall26.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66B1284-3406-5142-B2C8-F61A69296FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="27040" windowHeight="16980" activeTab="1" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="27040" windowHeight="16980" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 Fall" sheetId="1" r:id="rId1"/>

--- a/schedule-Fall26.xlsx
+++ b/schedule-Fall26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexander/GitHub/abuabara.github.io/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abuabara/GitHub/abuabara.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66B1284-3406-5142-B2C8-F61A69296FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735B47E7-A6FC-7644-9081-7DDD51947500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="27040" windowHeight="16980" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
+    <workbookView xWindow="0" yWindow="12580" windowWidth="27040" windowHeight="16980" activeTab="2" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 Fall" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="DAEN 300-301" sheetId="3" r:id="rId3"/>
     <sheet name="DAEN Capstone" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -752,7 +752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -783,7 +783,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2799,7 +2798,7 @@
       <c r="C21" t="s">
         <v>154</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" t="s">
         <v>155</v>
       </c>
     </row>
@@ -2953,7 +2952,7 @@
       <c r="C32" t="s">
         <v>183</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" t="s">
         <v>200</v>
       </c>
     </row>

--- a/schedule-Fall26.xlsx
+++ b/schedule-Fall26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abuabara/GitHub/abuabara.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735B47E7-A6FC-7644-9081-7DDD51947500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786221EE-938C-4B40-B3A3-F200F24DF964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12580" windowWidth="27040" windowHeight="16980" activeTab="2" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
+    <workbookView xWindow="0" yWindow="480" windowWidth="22940" windowHeight="14420" xr2:uid="{8FAF24E0-B87E-784E-B866-940FF89B59D3}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 Fall" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="223">
   <si>
     <t>M</t>
   </si>
@@ -110,9 +110,6 @@
     <t>Project</t>
   </si>
   <si>
-    <t>Introduction</t>
-  </si>
-  <si>
     <t>Bayesian thinking for risk and decision analysis</t>
   </si>
   <si>
@@ -155,66 +152,9 @@
     <t>Bayesian decision analysis and probabilistic forecasting</t>
   </si>
   <si>
-    <t>Team formation (part 1)</t>
-  </si>
-  <si>
-    <t>Sponsor matching</t>
-  </si>
-  <si>
-    <t>Decompose a problem (V model)</t>
-  </si>
-  <si>
-    <t>Decompose a problem (Toaster)</t>
-  </si>
-  <si>
-    <t>About reports (Toasters)</t>
-  </si>
-  <si>
     <t>Project charter</t>
   </si>
   <si>
-    <t>Problem definition</t>
-  </si>
-  <si>
-    <t>Requirements engineering</t>
-  </si>
-  <si>
-    <t>Standards engineering</t>
-  </si>
-  <si>
-    <t>Data acquisition / source evaluation</t>
-  </si>
-  <si>
-    <t>Advisor(s)</t>
-  </si>
-  <si>
-    <t>Ethics, privacy, and responsible data use</t>
-  </si>
-  <si>
-    <t>System architecture design</t>
-  </si>
-  <si>
-    <t>Design constraints and applicable standards</t>
-  </si>
-  <si>
-    <t>Project management (and Agile planning)</t>
-  </si>
-  <si>
-    <t>Initial technical prototype</t>
-  </si>
-  <si>
-    <t>Technical writing and documentation</t>
-  </si>
-  <si>
-    <t>Oral and visual presentation skills</t>
-  </si>
-  <si>
-    <t>Midpoint design review</t>
-  </si>
-  <si>
-    <t>Final proposal preparation</t>
-  </si>
-  <si>
     <t>Final presentations</t>
   </si>
   <si>
@@ -272,9 +212,6 @@
     <t>DAEN 459</t>
   </si>
   <si>
-    <t>DAEN/ISEN 427 / ISEN 627</t>
-  </si>
-  <si>
     <t>DAEN 300</t>
   </si>
   <si>
@@ -654,6 +591,123 @@
   </si>
   <si>
     <t>Working prototype, Midterm PRESENTATION 2</t>
+  </si>
+  <si>
+    <t>DAEN 427/ISEN 427/ISEN 627</t>
+  </si>
+  <si>
+    <t>Capstone expectations</t>
+  </si>
+  <si>
+    <t>Design process</t>
+  </si>
+  <si>
+    <t>Professional conduct</t>
+  </si>
+  <si>
+    <t>Team formation</t>
+  </si>
+  <si>
+    <t>Teamwork; roles and responsibilities</t>
+  </si>
+  <si>
+    <t>Sponsor engagement</t>
+  </si>
+  <si>
+    <t>Stakeholder analysis</t>
+  </si>
+  <si>
+    <t>Effective interviewing</t>
+  </si>
+  <si>
+    <t>Problem framing</t>
+  </si>
+  <si>
+    <t>Needs assessment; requirements elicitation</t>
+  </si>
+  <si>
+    <t>Scope definition; assumptions and constraints</t>
+  </si>
+  <si>
+    <t>Ethics, privacy, security, bias</t>
+  </si>
+  <si>
+    <t>Responsible data use</t>
+  </si>
+  <si>
+    <t>Data requirements</t>
+  </si>
+  <si>
+    <t>Data provenance; acquisition strategies</t>
+  </si>
+  <si>
+    <t>Applicable standards</t>
+  </si>
+  <si>
+    <t>Legal, organizational, and design constraints</t>
+  </si>
+  <si>
+    <t>Work breakdown structures</t>
+  </si>
+  <si>
+    <t>Project management</t>
+  </si>
+  <si>
+    <t>Estimation</t>
+  </si>
+  <si>
+    <t>Risk management</t>
+  </si>
+  <si>
+    <t>Feasibility</t>
+  </si>
+  <si>
+    <t>Change control</t>
+  </si>
+  <si>
+    <t>Alternatives</t>
+  </si>
+  <si>
+    <t>Evaluation planning</t>
+  </si>
+  <si>
+    <t>Metrics and acceptance criteria</t>
+  </si>
+  <si>
+    <t>Project reactivation; execution expectations</t>
+  </si>
+  <si>
+    <t>Configuration management</t>
+  </si>
+  <si>
+    <t>Reproducible development; repositories</t>
+  </si>
+  <si>
+    <t>Testing strategy</t>
+  </si>
+  <si>
+    <t>Data quality engineering</t>
+  </si>
+  <si>
+    <t>Validation and observability</t>
+  </si>
+  <si>
+    <t>Data transformation; integration</t>
+  </si>
+  <si>
+    <t>Metadata and lineage</t>
+  </si>
+  <si>
+    <t>Alternative designs</t>
+  </si>
+  <si>
+    <t>Trade-off analysis; design constraints</t>
+  </si>
+  <si>
+    <t>Interpretation; recommendations</t>
+  </si>
+  <si>
+    <t>Operational implications</t>
   </si>
 </sst>
 </file>
@@ -664,13 +718,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -687,36 +734,30 @@
       <name val="Frutiger LT Pro"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -752,37 +793,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1120,981 +1166,1051 @@
   <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="3" width="8.1640625" customWidth="1"/>
-    <col min="4" max="7" width="46.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="87.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="7.83203125" style="13" customWidth="1"/>
+    <col min="4" max="7" width="38.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="8"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>79</v>
+    <row r="1" spans="1:8" s="13" customFormat="1">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="14">
         <v>46258</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14">
+        <v>46260</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="16">
+        <v>46262</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14">
+        <v>46265</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3" t="s">
+      <c r="E5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4">
-        <v>46260</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C6" s="14">
+        <v>46267</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="16">
+        <v>46269</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14">
+        <v>46272</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="14">
+        <v>46274</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="16">
+        <v>46276</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14">
+        <v>46279</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11" t="s">
+        <v>215</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="14">
+        <v>46281</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="16">
+        <v>46283</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="14">
+        <v>46286</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" t="s">
+        <v>195</v>
+      </c>
+      <c r="F14" t="s">
+        <v>217</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="B15" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="14">
+        <v>46288</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="16">
+        <v>46290</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14">
+        <v>46293</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>196</v>
+      </c>
+      <c r="F17" t="s">
+        <v>137</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="B18" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="14">
+        <v>46295</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="16">
+        <v>46297</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="14">
+        <v>46300</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="B21" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="14">
+        <v>46302</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="16">
+        <v>46304</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="14">
+        <v>46307</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" t="s">
+        <v>143</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="B24" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="14">
+        <v>46309</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="16">
+        <v>46311</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="14">
+        <v>46314</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="B27" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="14">
+        <v>46316</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="16">
+        <v>46318</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="14">
+        <v>46321</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" t="s">
+        <v>200</v>
+      </c>
+      <c r="F29" t="s">
+        <v>219</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="B30" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="14">
+        <v>46323</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="16">
+        <v>46325</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="14">
+        <v>46328</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" t="s">
+        <v>203</v>
+      </c>
+      <c r="F32" t="s">
+        <v>151</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="B33" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="14">
+        <v>46330</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="16">
+        <v>46332</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="14">
+        <v>46335</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" t="s">
+        <v>205</v>
+      </c>
+      <c r="F35" t="s">
+        <v>221</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="B36" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="14">
+        <v>46337</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="15"/>
+      <c r="B37" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="16">
+        <v>46339</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="14">
+        <v>46342</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" t="s">
+        <v>209</v>
+      </c>
+      <c r="F38" t="s">
+        <v>156</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="B39" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="14">
+        <v>46344</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="15"/>
+      <c r="B40" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="16">
+        <v>46346</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="14">
+        <v>46349</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" t="s">
+        <v>117</v>
+      </c>
+      <c r="F41" t="s">
+        <v>159</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="B42" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="14">
+        <v>46351</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="15"/>
+      <c r="B43" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="16">
+        <v>46353</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="5"/>
+      <c r="G43" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="14">
+        <v>46356</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" t="s">
+        <v>120</v>
+      </c>
+      <c r="F44" t="s">
+        <v>161</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="B45" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="14">
+        <v>46357</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F45" s="6"/>
+      <c r="G45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H45" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="6">
-        <v>46262</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4">
-        <v>46265</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="1" t="s">
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="15"/>
+      <c r="B46" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="16">
+        <v>46358</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4">
-        <v>46267</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="6">
-        <v>46269</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4">
-        <v>46272</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4">
-        <v>46274</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="6">
-        <v>46276</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4">
-        <v>46279</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4">
-        <v>46281</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="6">
-        <v>46283</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="4">
-        <v>46286</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4">
-        <v>46288</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="6">
-        <v>46290</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="4">
-        <v>46293</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4">
-        <v>46295</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="6">
-        <v>46297</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="4">
-        <v>46300</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4">
-        <v>46302</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>46304</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4">
-        <v>46307</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="4">
-        <v>46309</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6">
-        <v>46311</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26" s="4">
-        <v>46314</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4">
-        <v>46316</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="6">
-        <v>46318</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29" s="4">
-        <v>46321</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="4">
-        <v>46323</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="6">
-        <v>46325</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="4">
-        <v>46328</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="4">
-        <v>46330</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>46332</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C35" s="4">
-        <v>46335</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="4">
-        <v>46337</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>46339</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C38" s="4">
-        <v>46342</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F38" s="12"/>
-      <c r="G38" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4">
-        <v>46344</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>46346</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C41" s="4">
-        <v>46349</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="4">
-        <v>46351</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>46353</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F43" s="11"/>
-      <c r="G43" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H43" s="14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C44" s="4">
-        <v>46356</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C45" s="4">
-        <v>46357</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H45" s="14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="6">
-        <v>46358</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F46" s="13"/>
-      <c r="G46" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H46" s="11" t="s">
+      <c r="F46" s="7"/>
+      <c r="G46" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="5" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -2108,12 +2224,12 @@
     <col min="2" max="2" width="46.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" t="s">
-        <v>199</v>
+    <row r="1" spans="1:3" s="10" customFormat="1">
+      <c r="A1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2121,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2129,7 +2245,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2137,7 +2253,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2145,7 +2261,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2153,7 +2269,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2161,7 +2277,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
@@ -2172,7 +2288,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2180,7 +2296,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2188,7 +2304,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2196,7 +2312,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2204,7 +2320,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2212,7 +2328,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
@@ -2223,7 +2339,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2231,7 +2347,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2239,7 +2355,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
@@ -2258,12 +2374,12 @@
     <col min="2" max="2" width="87.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" t="s">
-        <v>199</v>
+    <row r="1" spans="1:2" s="10" customFormat="1">
+      <c r="A1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2271,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2279,7 +2395,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2287,7 +2403,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2295,7 +2411,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2303,7 +2419,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2311,7 +2427,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2319,7 +2435,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2327,7 +2443,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2335,7 +2451,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2343,7 +2459,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2351,7 +2467,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2359,7 +2475,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2367,7 +2483,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2375,7 +2491,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2383,7 +2499,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2391,7 +2507,7 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2399,7 +2515,7 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2407,7 +2523,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2415,7 +2531,7 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2423,7 +2539,7 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2431,7 +2547,7 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2439,7 +2555,7 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2447,7 +2563,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2455,7 +2571,7 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2463,7 +2579,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2471,7 +2587,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2479,7 +2595,7 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2487,7 +2603,7 @@
         <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2495,7 +2611,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2503,7 +2619,7 @@
         <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2522,18 +2638,18 @@
     <col min="4" max="4" width="64.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D1" t="s">
-        <v>98</v>
+    <row r="1" spans="1:4" s="10" customFormat="1">
+      <c r="A1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2541,13 +2657,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2555,13 +2671,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2569,13 +2685,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2583,13 +2699,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2597,13 +2713,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2611,13 +2727,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2625,13 +2741,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2639,13 +2755,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2653,13 +2769,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2667,13 +2783,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2681,13 +2797,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2695,13 +2811,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2709,13 +2825,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2723,13 +2839,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2737,13 +2853,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2751,13 +2867,13 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2765,13 +2881,13 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2779,13 +2895,13 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2793,13 +2909,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2807,13 +2923,13 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C22" t="s">
-        <v>157</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>203</v>
+        <v>136</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2821,13 +2937,13 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="C23" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2835,13 +2951,13 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="D24" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2849,13 +2965,13 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
-        <v>165</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>204</v>
+        <v>144</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2863,13 +2979,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="C26" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="D26" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2877,13 +2993,13 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="C27" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2891,13 +3007,13 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="C28" t="s">
-        <v>173</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>202</v>
+        <v>152</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2905,13 +3021,13 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="C29" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D29" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2919,13 +3035,13 @@
         <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="C30" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="D30" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2933,13 +3049,13 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="C31" t="s">
-        <v>181</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2947,13 +3063,13 @@
         <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="C32" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="D32" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
